--- a/backend/templates/PurchaseOrder-ZRH.xlsx
+++ b/backend/templates/PurchaseOrder-ZRH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\erp\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7BD24B-1230-4E80-840F-7F10EB8370E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A70ED32-6771-480D-BC83-2796D48C3250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="2400" windowHeight="585" xr2:uid="{1CA8DE09-BC08-40D9-A06F-8907822E5FE4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ZRH" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">ZRH!$A$1:$L$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">ZRH!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -737,6 +737,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -766,30 +790,6 @@
     </xf>
     <xf numFmtId="182" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1175,7 +1175,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4.625" style="3" customWidth="1"/>
@@ -1193,20 +1193,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="98.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
     </row>
     <row r="2" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7"/>
@@ -1218,101 +1218,101 @@
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="58" t="s">
+      <c r="J2" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
     </row>
     <row r="3" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
       <c r="E3" s="40"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
-      <c r="J3" s="58" t="s">
+      <c r="J3" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
     </row>
     <row r="4" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
       <c r="E4" s="41"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="54" t="s">
+      <c r="J4" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
     </row>
     <row r="5" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
       <c r="E5" s="40"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="54" t="s">
+      <c r="J5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
       <c r="E6" s="40"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="54" t="s">
+      <c r="J6" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
     </row>
     <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="41"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="54" t="s">
+      <c r="J7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="54"/>
-      <c r="L7" s="54"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
     </row>
     <row r="8" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="9"/>
@@ -1324,11 +1324,11 @@
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
-      <c r="J8" s="46" t="s">
+      <c r="J8" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="48"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="56"/>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
@@ -1388,7 +1388,7 @@
       <c r="I10" s="19"/>
       <c r="J10" s="20"/>
       <c r="K10" s="21"/>
-      <c r="L10" s="45"/>
+      <c r="L10" s="53"/>
       <c r="M10" s="22"/>
       <c r="R10" s="23"/>
     </row>
@@ -1404,7 +1404,7 @@
       <c r="I11" s="19"/>
       <c r="J11" s="20"/>
       <c r="K11" s="21"/>
-      <c r="L11" s="45"/>
+      <c r="L11" s="53"/>
       <c r="M11" s="22"/>
       <c r="R11" s="20"/>
     </row>
@@ -1416,16 +1416,16 @@
       <c r="E12" s="24"/>
       <c r="F12" s="26"/>
       <c r="G12" s="27"/>
-      <c r="H12" s="49" t="s">
+      <c r="H12" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="50">
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="58">
         <f>SUM(K10:K11)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="50"/>
+      <c r="L12" s="58"/>
       <c r="P12" s="22"/>
       <c r="R12" s="28"/>
     </row>
@@ -1437,16 +1437,16 @@
       <c r="E13" s="24"/>
       <c r="F13" s="27"/>
       <c r="G13" s="26"/>
-      <c r="H13" s="49" t="s">
+      <c r="H13" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="51">
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="59">
         <f>K12</f>
         <v>0</v>
       </c>
-      <c r="L13" s="51"/>
+      <c r="L13" s="59"/>
       <c r="P13" s="22"/>
       <c r="R13" s="28"/>
     </row>
@@ -1610,7 +1610,9 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="30"/>
+      <c r="A25" s="30" t="s">
+        <v>45</v>
+      </c>
       <c r="B25" s="29"/>
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
@@ -1621,110 +1623,96 @@
       <c r="I25" s="36"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="36"/>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="1:12" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="37" t="s">
+    <row r="26" spans="1:12" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="37" t="s">
         <v>42</v>
       </c>
+      <c r="C26"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="J26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="38"/>
+      <c r="B27" s="38"/>
       <c r="C27"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="J27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27" s="39"/>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="37" t="s">
+        <v>30</v>
+      </c>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
       <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28" s="39"/>
+      <c r="J28" s="37" t="s">
+        <v>31</v>
+      </c>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="37" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
       <c r="F29"/>
       <c r="J29" s="37" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="J30" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="43"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="44"/>
-      <c r="J31" s="44"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="44"/>
+    <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="51"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="J7:L7"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:L13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.47" bottom="0.2" header="0.51" footer="0.31"/>
-  <pageSetup paperSize="9" scale="74" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="76" orientation="landscape" r:id="rId1"/>
   <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddFooter>&amp;C第 &amp;P 页，共 &amp;N 页</oddFooter>
   </headerFooter>

--- a/backend/templates/PurchaseOrder-ZRH.xlsx
+++ b/backend/templates/PurchaseOrder-ZRH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\erp\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A70ED32-6771-480D-BC83-2796D48C3250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6346E25-DAB4-484A-8AF5-5C2CA261123F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="2400" windowHeight="585" xr2:uid="{1CA8DE09-BC08-40D9-A06F-8907822E5FE4}"/>
   </bookViews>
@@ -737,6 +737,48 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -748,48 +790,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -806,85 +806,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>1066800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56323" name="图片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CBE0A8F-BAB8-FB72-7878-03726623DD94}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6886575" y="1066800"/>
-          <a:ext cx="3810000" cy="1552575"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1193,20 +1114,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="98.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
     </row>
     <row r="2" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7"/>
@@ -1218,101 +1139,101 @@
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="40"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
     </row>
     <row r="4" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
       <c r="E4" s="41"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
-      <c r="J4" s="48" t="s">
+      <c r="J4" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
     </row>
     <row r="5" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="40"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="48" t="s">
+      <c r="J5" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
     </row>
     <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="40"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="48" t="s">
+      <c r="J6" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
     </row>
     <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="41"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="48" t="s">
+      <c r="J7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
     </row>
     <row r="8" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="9"/>
@@ -1324,11 +1245,11 @@
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
-      <c r="J8" s="54" t="s">
+      <c r="J8" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="K8" s="55"/>
-      <c r="L8" s="56"/>
+      <c r="K8" s="47"/>
+      <c r="L8" s="48"/>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
@@ -1388,7 +1309,7 @@
       <c r="I10" s="19"/>
       <c r="J10" s="20"/>
       <c r="K10" s="21"/>
-      <c r="L10" s="53"/>
+      <c r="L10" s="45"/>
       <c r="M10" s="22"/>
       <c r="R10" s="23"/>
     </row>
@@ -1404,7 +1325,7 @@
       <c r="I11" s="19"/>
       <c r="J11" s="20"/>
       <c r="K11" s="21"/>
-      <c r="L11" s="53"/>
+      <c r="L11" s="45"/>
       <c r="M11" s="22"/>
       <c r="R11" s="20"/>
     </row>
@@ -1416,16 +1337,16 @@
       <c r="E12" s="24"/>
       <c r="F12" s="26"/>
       <c r="G12" s="27"/>
-      <c r="H12" s="57" t="s">
+      <c r="H12" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="58">
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="50">
         <f>SUM(K10:K11)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="58"/>
+      <c r="L12" s="50"/>
       <c r="P12" s="22"/>
       <c r="R12" s="28"/>
     </row>
@@ -1437,16 +1358,16 @@
       <c r="E13" s="24"/>
       <c r="F13" s="27"/>
       <c r="G13" s="26"/>
-      <c r="H13" s="57" t="s">
+      <c r="H13" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="59">
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="51">
         <f>K12</f>
         <v>0</v>
       </c>
-      <c r="L13" s="59"/>
+      <c r="L13" s="51"/>
       <c r="P13" s="22"/>
       <c r="R13" s="28"/>
     </row>
@@ -1628,9 +1549,9 @@
         <v>42</v>
       </c>
       <c r="C26"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
       <c r="J26" t="s">
         <v>43</v>
       </c>
@@ -1673,21 +1594,33 @@
       <c r="L29" s="3"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="51"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="52"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="J7:L7"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="L10:L11"/>
@@ -1696,18 +1629,6 @@
     <mergeCell ref="K12:L12"/>
     <mergeCell ref="H13:J13"/>
     <mergeCell ref="K13:L13"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="J4:L4"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -1716,6 +1637,5 @@
   <headerFooter scaleWithDoc="0" alignWithMargins="0">
     <oddFooter>&amp;C第 &amp;P 页，共 &amp;N 页</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>